--- a/docs/design/ACSMS-SCR-020/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_口座振替データ出力画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-020/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_口座振替データ出力画面_V1.0.xlsx
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG5"/>
+  <dimension ref="A1:AG6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1667,19 +1667,75 @@
       <c r="AF5" s="10" t="n"/>
       <c r="AG5" s="11" t="n"/>
     </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="11" t="n"/>
+      <c r="R6" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-08（#56600）：集計対象を**紙版(1)と電子版(2)のみ**に限定。電子版は**承認済（denshi_shonin_status = 1）かつ有料（denshi_dokusya_shubetsu = 1）**に限る（未承認・無料は購読料が発生せず引き落とす対象が無いため）。**併読(3)は対象外**。従来は購読種別で一切絞っておらず、併読も無料の電子版も口座引落の対象になり得た。集計SQLと失効単価チェックSQLの双方に条件を追加する — 片方だけだと「引落対象ではない購読者が参照する失効単価でエラーになり出力できない」という不整合が起きるため。</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="10" t="n"/>
+      <c r="V6" s="11" t="n"/>
+      <c r="W6" s="17" t="inlineStr"/>
+      <c r="X6" s="10" t="n"/>
+      <c r="Y6" s="10" t="n"/>
+      <c r="Z6" s="10" t="n"/>
+      <c r="AA6" s="11" t="n"/>
+      <c r="AB6" s="17" t="inlineStr"/>
+      <c r="AC6" s="10" t="n"/>
+      <c r="AD6" s="10" t="n"/>
+      <c r="AE6" s="10" t="n"/>
+      <c r="AF6" s="10" t="n"/>
+      <c r="AG6" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="42">
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="R5:V5"/>
+    <mergeCell ref="W6:AA6"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="W5:AA5"/>
     <mergeCell ref="R4:V4"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="R6:V6"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="K3:Q3"/>
     <mergeCell ref="W4:AA4"/>
@@ -1695,6 +1751,7 @@
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AB3:AG3"/>
     <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="AB5:AG5"/>
@@ -1704,6 +1761,7 @@
     <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1876,7 +1934,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2392,7 +2450,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3207,7 +3265,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3764,7 +3822,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -5853,7 +5911,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8444,6 +8502,11 @@
  WHERE d.deleted_at IS NULL
    AND d.shiharai_hoho = 1
    AND d.tetsuzuki_shurui = 1
+   -- 集計対象は紙版(1)と電子版(2)のみ。電子版は承認済かつ有料に限る（#56600）
+   AND ( d.dokusya_shubetsu = 1
+      OR (d.dokusya_shubetsu = 2
+          AND d.denshi_shonin_status = 1
+          AND d.denshi_dokusya_shubetsu = 1) )
    AND d.dokusya_kaishi_date &lt;= :target_month
    AND (d.dokusya_chushi_date IS NULL OR d.dokusya_chushi_date &gt; :target_month)
    AND d.ja_id = :user_ja_id
@@ -8539,6 +8602,11 @@
  WHERE d.deleted_at IS NULL
    AND d.shiharai_hoho = 1
    AND d.tetsuzuki_shurui = 1
+   -- 集計対象は紙版(1)と電子版(2)のみ。電子版は承認済かつ有料に限る（#56600）
+   AND ( d.dokusya_shubetsu = 1
+      OR (d.dokusya_shubetsu = 2
+          AND d.denshi_shonin_status = 1
+          AND d.denshi_dokusya_shubetsu = 1) )
    AND d.dokusya_kaishi_date &lt;= :target_month
    AND (d.dokusya_chushi_date IS NULL OR d.dokusya_chushi_date &gt; :target_month)
    /* DataScope */
@@ -9476,7 +9544,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -11437,7 +11505,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>

--- a/docs/design/ACSMS-SCR-020/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_口座振替データ出力画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-020/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_口座振替データ出力画面_V1.0.xlsx
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG6"/>
+  <dimension ref="A1:AG7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1718,23 +1718,78 @@
       <c r="AF6" s="10" t="n"/>
       <c r="AG6" s="11" t="n"/>
     </row>
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="11" t="n"/>
+      <c r="R7" s="19" t="inlineStr">
+        <is>
+          <t>実装との整合更新（API-020-002）：ダウンロード名を全銀メディア受入名の固定値 `ZENOUTFD` から引落日ベースの説明的名称 `口座振替データ_YYYY年MM月DD日`（拡張子なし、ja_code・タイムスタンプなし）へ変更。t_file_download.file_name（SCR-022再DL名）も同名に統一。応答 Content-Type を `text/plain; charset=Shift_JIS` から **`application/octet-stream`** に変更（拡張子なしファイル名だと text/plain 等の既知タイプではブラウザが `.txt` を自動付与してしまうため）。S3保存名（内部）は従来通り `口座振替データ_{ja_code}_{YYYY}年{MM}月{DD}日_{タイムスタンプ}`（拡張子なし）で一意化。</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="11" t="n"/>
+      <c r="W7" s="17" t="inlineStr"/>
+      <c r="X7" s="10" t="n"/>
+      <c r="Y7" s="10" t="n"/>
+      <c r="Z7" s="10" t="n"/>
+      <c r="AA7" s="11" t="n"/>
+      <c r="AB7" s="17" t="inlineStr"/>
+      <c r="AC7" s="10" t="n"/>
+      <c r="AD7" s="10" t="n"/>
+      <c r="AE7" s="10" t="n"/>
+      <c r="AF7" s="10" t="n"/>
+      <c r="AG7" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="49">
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="R5:V5"/>
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="C5:G5"/>
+    <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="W5:AA5"/>
     <mergeCell ref="R4:V4"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="H7:J7"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="C4:G4"/>
+    <mergeCell ref="R7:V7"/>
     <mergeCell ref="K4:Q4"/>
     <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="R6:V6"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="K3:Q3"/>
@@ -1743,8 +1798,10 @@
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="K5:Q5"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="W7:AA7"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="A5:B5"/>
@@ -1754,6 +1811,7 @@
     <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="W2:AA2"/>
     <mergeCell ref="H4:J4"/>
@@ -1934,7 +1992,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2450,7 +2508,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3265,7 +3323,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3822,7 +3880,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -5911,7 +5969,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8704,24 +8762,24 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="18" customHeight="1">
+    <row r="116" ht="72" customHeight="1">
       <c r="C116" s="41" t="inlineStr">
         <is>
-          <t>v1.1: ダウンロード名は全銀メディア受入名の**固定値 `ZENOUTFD`（拡張子なし）**。</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="36" customHeight="1">
+          <t>v1.3（2026/08/13）: ダウンロード名（＝t_file_download.file_name）は引落日ベースの**説明的名称 `口座振替データ_YYYY年MM月DD日`（拡張子なし、ja_code・タイムスタンプなし）**。旧版の全銀メディア受入名固定値 `ZENOUTFD` は撤廃した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="54" customHeight="1">
       <c r="C117" s="41" t="inlineStr">
         <is>
-          <t>生成したファイルを共通のファイルアーカイブサービス（FileArchiveService）経由でS3に保存する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="54" customHeight="1">
+          <t>生成したファイルを共通のファイルアーカイブサービス（FileArchiveService）経由でS3に保存する。`displayName`（上記ダウンロード名）を指定し、S3保存名とDL表示名を分離する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="72" customHeight="1">
       <c r="D118" s="41" t="inlineStr">
         <is>
-          <t>S3キー: `koza-furikae/{ja_code}/{YYYY}/{baseName}_{yyyyMMddHHmmss}`（`baseName` = `口座振替データ_{ja_code}_{YYYY}年{MM}月{DD}日`、拡張子なし）。</t>
+          <t>S3キー: `koza-furikae/{ja_code}/{YYYY}/{baseName}_{yyyyMMddHHmmss}`（`baseName` = `口座振替データ_{ja_code}_{YYYY}年{MM}月{DD}日`、拡張子なし。ja_code・タイムスタンプ付きで一意化する内部保管用の名称であり、ダウンロード名とは異なる）。</t>
         </is>
       </c>
     </row>
@@ -8965,7 +9023,7 @@
   "jastem_toriatsukai_tenpo_code": "001",
   "jastem_tyokin_shubetsu": "1",
   "jastem_koza_no": "*******",
-  "file_name": "口座振替データ_JA1301_2026年05月27日_20260522103000",
+  "file_name": "口座振替データ_2026年05月27日",
   "s3_file_path": "koza-furikae/JA1301/2026/口座振替データ_JA1301_2026年05月27日_20260522103000",
   "record_count": 2
 }</t>
@@ -9020,17 +9078,17 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="18" customHeight="1">
+    <row r="133" ht="54" customHeight="1">
       <c r="C133" s="41" t="inlineStr">
         <is>
-          <t>`Content-Type: text/plain; charset=Shift_JIS`</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="36" customHeight="1">
+          <t>`Content-Type: application/octet-stream`（拡張子なしファイル名で text/plain 等の既知タイプだとブラウザが `.txt` を自動付与してしまうため固定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="72" customHeight="1">
       <c r="C134" s="41" t="inlineStr">
         <is>
-          <t>`Content-Disposition: attachment; filename="ZENOUTFD"; filename*=UTF-8''ZENOUTFD`（拡張子なし固定名）</t>
+          <t>`Content-Disposition: attachment; filename="&lt;ASCIIフォールバック名&gt;"; filename*=UTF-8''&lt;パーセントエンコードした表示名&gt;`（表示名は `口座振替データ_YYYY年MM月DD日`、拡張子なし。ASCIIフォールバック名は表示名の非ASCII文字をアンダースコアへ置換した文字列）</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9602,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -11505,7 +11563,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
